--- a/MainTop/13.07.2026 Таня Озон/print_sorted.xlsx
+++ b/MainTop/13.07.2026 Таня Озон/print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\13.07.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\13.07.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83DAF2C-3467-4DF6-A943-5AEFB377FB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC26D71-0226-499D-A151-0F4AF8825A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1059,14 +1070,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S192"/>
+  <dimension ref="A1:S193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" customWidth="1"/>
-    <col min="2" max="16" width="6.140625" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" customWidth="1"/>
-    <col min="19" max="19" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4.42578125" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="8" max="8" width="3.5703125" customWidth="1"/>
+    <col min="9" max="10" width="3.140625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" customWidth="1"/>
+    <col min="14" max="14" width="3.5703125" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" customWidth="1"/>
+    <col min="16" max="16" width="3.42578125" customWidth="1"/>
+    <col min="17" max="18" width="0.140625" customWidth="1"/>
+    <col min="19" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -12397,7 +12419,78 @@
         <v>21</v>
       </c>
     </row>
+    <row r="193" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B193">
+        <f>SUM(B2:B192)</f>
+        <v>108</v>
+      </c>
+      <c r="C193">
+        <f t="shared" ref="C193:R193" si="0">SUM(C2:C192)</f>
+        <v>101</v>
+      </c>
+      <c r="D193">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="E193">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="F193">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="G193">
+        <f t="shared" si="0"/>
+        <v>337</v>
+      </c>
+      <c r="H193">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="I193">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="J193">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="K193">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L193">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="M193">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="N193">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="O193">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="P193">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="Q193">
+        <f t="shared" si="0"/>
+        <v>1606</v>
+      </c>
+      <c r="R193">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>